--- a/Parameters.xlsx
+++ b/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hogeschoolutrecht-my.sharepoint.com/personal/luuk_netten_student_hu_nl/Documents/1. School/Merwede_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djens\Downloads\simulatie-s-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_F25DC773A252ABDACC104848E19D49AA5BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BAC8973-AB56-40E6-A092-7CF499AD4428}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F90BE1-E9CD-4BEC-BAB5-846234DB2034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -95,6 +95,85 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>31750</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>44450</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1026" name="Button 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1026"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="36576" rIns="36576" bIns="36576" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="nl-NL" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri"/>
+                  <a:ea typeface="Calibri"/>
+                  <a:cs typeface="Calibri"/>
+                </a:rPr>
+                <a:t>Knop 2</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -359,15 +438,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Blad1"/>
   <dimension ref="A2:B3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -375,7 +455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -385,5 +465,35 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1026" r:id="rId3" name="Button 2">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!Knop2_Klikken">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>1</xdr:row>
+                    <xdr:rowOff>31750</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>44450</xdr:colOff>
+                    <xdr:row>1</xdr:row>
+                    <xdr:rowOff>171450</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
 </worksheet>
 </file>
--- a/Parameters.xlsx
+++ b/Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djens\Downloads\simulatie-s-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F90BE1-E9CD-4BEC-BAB5-846234DB2034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC9CA63-E5BD-4DD6-8E01-49A0E69CC806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -107,26 +107,26 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor>
         <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>590550</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>19050</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>31750</xdr:rowOff>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>44450</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>533400</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1026" name="Button 2" hidden="1">
+            <xdr:cNvPr id="1027" name="Button 3" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1026"/>
+                  <a14:compatExt spid="_x0000_s1027"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -148,7 +148,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="36576" rIns="36576" bIns="36576" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -163,7 +163,7 @@
                   <a:ea typeface="Calibri"/>
                   <a:cs typeface="Calibri"/>
                 </a:rPr>
-                <a:t>Knop 2</a:t>
+                <a:t>Knop 3</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -441,13 +441,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Blad1"/>
   <dimension ref="A2:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -455,7 +455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -472,20 +472,20 @@
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1026" r:id="rId3" name="Button 2">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!Knop2_Klikken">
+            <control shapeId="1027" r:id="rId3" name="Button 3">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!Knop3_Klikken">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
-                    <xdr:col>2</xdr:col>
-                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>19050</xdr:colOff>
                     <xdr:row>1</xdr:row>
-                    <xdr:rowOff>31750</xdr:rowOff>
+                    <xdr:rowOff>66675</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>44450</xdr:colOff>
-                    <xdr:row>1</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>533400</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
